--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119102216</v>
+        <v>136949521</v>
       </c>
       <c r="B3" t="n">
-        <v>102419</v>
+        <v>110333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,57 +838,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>58</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hallonstugan, gullklöver  vid vägen, Srm</t>
+          <t>Barksätter, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562364</v>
+        <v>562195</v>
       </c>
       <c r="R3" t="n">
-        <v>6537591</v>
+        <v>6537739</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,24 +894,14 @@
           <t>Östra Vingåker</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>D-Kat-0630</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 dellokaler</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,65 +910,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Artificiell miljö</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>vägslänter</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Saga Samuelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119102216</t>
+          <t>https://artportalen.se/Sighting/136949521</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87523417</v>
+        <v>136949522</v>
       </c>
       <c r="B4" t="n">
-        <v>102443</v>
+        <v>106406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221333</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1002,37 +965,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hallonstugan backklöver 50 m so, Srm</t>
+          <t>Skalltorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562424</v>
+        <v>562417</v>
       </c>
       <c r="R4" t="n">
-        <v>6537538</v>
+        <v>6537535</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1057,19 +1000,14 @@
           <t>Östra Vingåker</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>D-Kat-0544</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,85 +1016,95 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>vägslänt</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Saga Samuelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87523417</t>
+          <t>https://artportalen.se/Sighting/136949522</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6333202</v>
+        <v>119102216</v>
       </c>
       <c r="B5" t="n">
-        <v>106650</v>
+        <v>102419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>225197</v>
+        <v>221317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äkta ljungsnärja</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bokvarn, 850 m NV, hagmark, Hallonstugans grund, Srm</t>
+          <t>Hallonstugan, gullklöver  vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562437</v>
+        <v>562364</v>
       </c>
       <c r="R5" t="n">
-        <v>6537538</v>
+        <v>6537591</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1178,19 +1126,24 @@
           <t>Östra Vingåker</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D-Kat-0630</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1995-08-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1995-08-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hagmark kring f.d. Hallonstugan</t>
+          <t>2 dellokaler</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,32 +1152,508 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>betesmark</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
+          <t>vägslänter</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119102216</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87523417</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallonstugan backklöver 50 m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6537538</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D-Kat-0544</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87523417</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136949889</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skalltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562417</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6537535</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Finns lite här och där längs hela slänten</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949889</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136949523</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skalltorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562482</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6537485</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949523</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6333202</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106650</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>225197</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Äkta ljungsnärja</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bokvarn, 850 m NV, hagmark, Hallonstugans grund, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562437</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6537538</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1995-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1995-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hagmark kring f.d. Hallonstugan</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>betesmark</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6333202</t>
         </is>
@@ -1236,6 +1665,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>136949521</v>
       </c>
       <c r="B3" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>136949522</v>
       </c>
       <c r="B4" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136949889</v>
       </c>
       <c r="B7" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136949523</v>
       </c>
       <c r="B8" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>136949521</v>
       </c>
       <c r="B3" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>136949522</v>
       </c>
       <c r="B4" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136949889</v>
       </c>
       <c r="B7" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136949523</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -830,7 +830,7 @@
         <v>136949521</v>
       </c>
       <c r="B3" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>136949522</v>
       </c>
       <c r="B4" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136949889</v>
       </c>
       <c r="B7" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136949523</v>
       </c>
       <c r="B8" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
